--- a/data/trans_camb/P3A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -624,47 +624,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>13,78</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>21,86</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>37,34</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,16</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>10,06</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,17</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>12,61</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>24,86</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,61; 18,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,66; 26,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>31,58; 42,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,18; 4,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,34; 6,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,13; 13,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,4; 10,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,55; 16,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,93; 28,84</t>
         </is>
       </c>
     </row>
@@ -730,47 +730,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>143,93%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,42%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30,21; 80,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>58,04; 114,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>111,4; 184,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,71; 5,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,38; 8,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,29; 16,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,02; 20,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,29; 30,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,14; 54,83</t>
         </is>
       </c>
     </row>
@@ -840,47 +840,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>10,91</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>19,91</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>20,49</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-3,42</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,2</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>6,19</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,8</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>11,65</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>11,06</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,27; 15,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,64; 24,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,81; 35,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,77; 0,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,31; 6,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,37; 9,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,63; 6,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,47; 14,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,15; 21,0</t>
         </is>
       </c>
     </row>
@@ -946,47 +946,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-3,98%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,43; 53,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,72; 85,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,31; 116,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,77; 0,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,35; 7,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,86; 10,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,04; 11,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,96; 25,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-20,29; 36,15</t>
         </is>
       </c>
     </row>
@@ -1056,47 +1056,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,84</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>12,69</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>28,28</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,78</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>18,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,7; 9,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,03; 17,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,13; 33,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,24; 2,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,16; 4,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,59; 10,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,36; 5,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,61; 10,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,58; 25,35</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,04%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,96; 26,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,98; 49,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>53,0; 93,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,94; 2,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,44; 5,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,95; 12,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,65; 8,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,56; 17,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,56; 41,57</t>
         </is>
       </c>
     </row>
@@ -1272,47 +1272,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>8,96</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>20,38</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>27,83</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,19</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>4,67</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,53</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>12,22</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>17,53</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,73; 13,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,14; 24,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,72; 32,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,1; 5,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,62; 8,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,96; 11,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,41; 8,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,3; 15,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,19; 21,02</t>
         </is>
       </c>
     </row>
@@ -1378,47 +1378,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,78; 35,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,15; 66,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>54,61; 88,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,31; 7,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,94; 10,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,85; 14,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,8; 14,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,62; 25,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,71; 35,45</t>
         </is>
       </c>
     </row>
@@ -1488,47 +1488,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>9,46</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>18,92</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>27,11</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,48</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>4,46</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>11,13</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>17,45</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,99; 11,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,18; 21,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,96; 32,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,25; 1,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,64; 5,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,81; 9,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,73; 6,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,59; 12,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,8; 20,9</t>
         </is>
       </c>
     </row>
@@ -1594,47 +1594,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,64%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,42; 36,42</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,58; 64,3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,95; 97,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,65; 1,67</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,93; 6,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,81; 11,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,55; 10,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,77; 21,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,69; 35,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37,34</t>
+          <t>36,67</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,06</t>
+          <t>9,56</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24,86</t>
+          <t>23,73</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,61; 18,99</t>
+          <t>8,45; 18,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,66; 26,65</t>
+          <t>16,81; 27,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,58; 42,83</t>
+          <t>30,82; 41,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 4,42</t>
+          <t>-3,57; 4,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 6,94</t>
+          <t>-0,23; 6,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,13; 13,46</t>
+          <t>6,35; 12,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 10,98</t>
+          <t>3,58; 10,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,55; 16,05</t>
+          <t>8,97; 16,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,93; 28,84</t>
+          <t>19,93; 26,64</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>143,93%</t>
+          <t>141,36%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,21; 80,67</t>
+          <t>29,27; 78,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,04; 114,67</t>
+          <t>59,09; 114,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>111,4; 184,74</t>
+          <t>106,61; 180,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 5,38</t>
+          <t>-4,22; 5,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 8,53</t>
+          <t>-0,41; 8,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,29; 16,49</t>
+          <t>7,4; 15,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 20,68</t>
+          <t>6,41; 20,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,29; 30,4</t>
+          <t>15,63; 31,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,14; 54,83</t>
+          <t>35,35; 50,36</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20,49</t>
+          <t>33,6</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,19</t>
+          <t>5,97</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,06</t>
+          <t>19,84</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,27; 15,25</t>
+          <t>6,98; 16,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,64; 24,88</t>
+          <t>15,22; 24,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 35,42</t>
+          <t>29,33; 38,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 0,06</t>
+          <t>-6,9; -0,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 6,25</t>
+          <t>0,38; 6,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 9,08</t>
+          <t>3,15; 8,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,81</t>
+          <t>0,83; 7,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 14,68</t>
+          <t>8,46; 14,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 21,0</t>
+          <t>17,01; 22,91</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>107,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,43; 53,4</t>
+          <t>20,75; 55,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,72; 85,68</t>
+          <t>45,27; 85,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,31; 116,2</t>
+          <t>87,2; 134,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 0,07</t>
+          <t>-7,91; -0,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 7,38</t>
+          <t>0,44; 7,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 10,87</t>
+          <t>3,7; 10,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 11,92</t>
+          <t>1,25; 12,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,96; 25,77</t>
+          <t>14,04; 25,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 36,15</t>
+          <t>28,01; 40,47</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28,28</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,16</t>
+          <t>3,64</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18,97</t>
+          <t>15,9</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 9,77</t>
+          <t>-1,66; 8,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,03; 17,94</t>
+          <t>6,81; 17,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,13; 33,87</t>
+          <t>22,01; 33,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 2,18</t>
+          <t>-5,42; 1,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 4,78</t>
+          <t>-1,96; 4,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 10,66</t>
+          <t>-0,08; 7,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 5,01</t>
+          <t>-2,66; 4,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 10,71</t>
+          <t>3,68; 10,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,58; 25,35</t>
+          <t>12,42; 19,39</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 26,74</t>
+          <t>-3,84; 24,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,98; 49,57</t>
+          <t>16,27; 47,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53,0; 93,46</t>
+          <t>51,55; 90,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 2,53</t>
+          <t>-6,1; 2,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 5,62</t>
+          <t>-2,21; 5,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 12,64</t>
+          <t>-0,08; 8,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 8,31</t>
+          <t>-4,07; 8,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,56; 17,56</t>
+          <t>5,64; 17,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,56; 41,57</t>
+          <t>19,01; 31,5</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27,83</t>
+          <t>26,94</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,53</t>
+          <t>7,02</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17,53</t>
+          <t>16,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 13,48</t>
+          <t>4,15; 13,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,14; 24,42</t>
+          <t>16,26; 25,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,72; 32,14</t>
+          <t>22,5; 31,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 5,5</t>
+          <t>-1,27; 5,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,19</t>
+          <t>0,95; 7,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,96; 11,22</t>
+          <t>3,64; 10,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,41; 8,52</t>
+          <t>2,18; 8,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,3; 15,1</t>
+          <t>9,54; 15,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,19; 21,02</t>
+          <t>13,48; 19,5</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,78; 35,75</t>
+          <t>9,74; 35,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36,15; 66,03</t>
+          <t>39,06; 68,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54,61; 88,24</t>
+          <t>54,06; 85,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 7,04</t>
+          <t>-1,53; 7,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,94; 10,38</t>
+          <t>1,15; 9,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,85; 14,32</t>
+          <t>4,41; 13,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,8; 14,21</t>
+          <t>3,48; 14,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,62; 25,33</t>
+          <t>14,98; 25,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22,71; 35,45</t>
+          <t>21,37; 32,99</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27,11</t>
+          <t>31,28</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,48</t>
+          <t>6,56</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17,45</t>
+          <t>18,9</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,99; 11,99</t>
+          <t>6,86; 11,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,18; 21,09</t>
+          <t>16,48; 21,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,96; 32,59</t>
+          <t>28,77; 33,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,38</t>
+          <t>-2,22; 1,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,1</t>
+          <t>1,57; 4,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,81; 9,37</t>
+          <t>4,99; 8,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,16</t>
+          <t>2,91; 6,23</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,59; 12,75</t>
+          <t>9,43; 12,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,8; 20,9</t>
+          <t>17,31; 20,54</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>19,42; 36,42</t>
+          <t>19,42; 35,92</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>45,58; 64,3</t>
+          <t>46,31; 64,22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35,95; 97,21</t>
+          <t>80,67; 101,88</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,67</t>
+          <t>-2,63; 1,71</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,15</t>
+          <t>1,85; 5,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,81; 11,19</t>
+          <t>5,86; 9,83</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,55; 10,5</t>
+          <t>4,79; 10,62</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15,77; 21,72</t>
+          <t>15,58; 21,74</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>14,69; 35,4</t>
+          <t>28,61; 35,25</t>
         </is>
       </c>
     </row>
